--- a/backend/PDF_DOC/CBIC/Rules/CUSTOMS RULES.xlsx
+++ b/backend/PDF_DOC/CBIC/Rules/CUSTOMS RULES.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C55A34-80E2-4816-9AF1-3417BDF775C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AAEC96-D3A7-4EA3-B66C-7D386BAFB79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" firstSheet="29" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,6 +41,7 @@
     <sheet name="Customs-Central DBK Rules,2017" sheetId="32" r:id="rId31"/>
     <sheet name="Customs,CentralExciseRules,1995" sheetId="33" r:id="rId32"/>
     <sheet name="DeferredPaymentofImportDuty2016" sheetId="34" r:id="rId33"/>
+    <sheet name="Sheet1" sheetId="35" r:id="rId34"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45276,7 +45277,7 @@
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B121" s="1"/>
     </row>
-    <row r="122" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
         <v>3637</v>
       </c>
@@ -45675,7 +45676,7 @@
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
     </row>
-    <row r="210" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A210" s="5"/>
       <c r="B210" s="5" t="s">
         <v>3683</v>
@@ -46453,7 +46454,7 @@
     <row r="428" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B428" s="5"/>
     </row>
-    <row r="429" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B429" s="5" t="s">
         <v>3777</v>
       </c>
@@ -46479,7 +46480,7 @@
         <v>3780</v>
       </c>
     </row>
-    <row r="435" spans="2:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:2" ht="60" x14ac:dyDescent="0.25">
       <c r="B435" s="5" t="s">
         <v>3781</v>
       </c>
@@ -46527,7 +46528,7 @@
     <row r="446" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B446" s="5"/>
     </row>
-    <row r="447" spans="2:2" ht="150" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:2" ht="135" x14ac:dyDescent="0.25">
       <c r="B447" s="5" t="s">
         <v>3787</v>
       </c>
@@ -46615,7 +46616,7 @@
     <row r="468" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B468" s="5"/>
     </row>
-    <row r="469" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B469" s="5" t="s">
         <v>3798</v>
       </c>
@@ -46684,7 +46685,7 @@
     <row r="485" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B485" s="5"/>
     </row>
-    <row r="486" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B486" s="5" t="s">
         <v>3807</v>
       </c>
@@ -46732,7 +46733,7 @@
     <row r="497" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B497" s="5"/>
     </row>
-    <row r="498" spans="2:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B498" s="5" t="s">
         <v>3813</v>
       </c>
@@ -48909,7 +48910,7 @@
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
     </row>
-    <row r="165" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
       <c r="B165" s="5" t="s">
         <v>4045</v>
@@ -50464,6 +50465,15 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45902FF1-67BB-48EC-A244-73B2F8167A39}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
